--- a/重点商品CA別進捗_2026年5月.xlsx
+++ b/重点商品CA別進捗_2026年5月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +213,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -239,25 +239,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -284,18 +272,6 @@
               </pt>
               <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -359,6 +335,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -409,7 +393,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -435,25 +419,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -480,18 +452,6 @@
               </pt>
               <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -555,6 +515,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -605,7 +573,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -625,28 +593,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -666,21 +619,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>0</v>
               </pt>
             </numLit>
@@ -745,6 +683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -795,7 +741,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -815,28 +761,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -856,21 +787,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>0</v>
               </pt>
             </numLit>
@@ -935,6 +851,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -985,7 +909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1005,28 +929,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1046,21 +955,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1125,6 +1019,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1175,7 +1077,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1195,28 +1097,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1237,21 +1124,6 @@
               </pt>
               <pt idx="6">
                 <v>2</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1315,6 +1187,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1365,7 +1245,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1385,28 +1265,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1426,22 +1291,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>3</v>
-              </pt>
-              <pt idx="7">
-                <v>3</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
+                <v>8</v>
               </pt>
             </numLit>
           </val>
@@ -1487,7 +1337,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1505,6 +1355,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1555,7 +1413,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1575,28 +1433,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1616,22 +1459,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
+                <v>4</v>
               </pt>
             </numLit>
           </val>
@@ -1677,7 +1505,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1695,6 +1523,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1745,7 +1581,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1765,28 +1601,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1806,21 +1627,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1885,6 +1691,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1935,7 +1749,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1955,28 +1769,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -1996,22 +1795,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2075,6 +1859,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2125,7 +1917,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2145,28 +1937,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2186,21 +1963,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>1</v>
               </pt>
             </numLit>
@@ -2265,6 +2027,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2315,7 +2085,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -2341,25 +2111,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2385,19 +2143,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -2461,6 +2207,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2511,7 +2265,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2531,28 +2285,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="9">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="12"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2572,21 +2311,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2651,6 +2375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2701,7 +2433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2718,19 +2450,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
@@ -2748,12 +2474,6 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2817,6 +2537,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2867,7 +2595,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2884,19 +2612,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2913,12 +2635,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2983,6 +2699,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3033,7 +2757,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3050,19 +2774,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -3079,12 +2797,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3149,6 +2861,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3199,7 +2919,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3216,19 +2936,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
@@ -3245,13 +2959,7 @@
                 <v>3</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
                 <v>2</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3315,6 +3023,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3365,7 +3081,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3382,19 +3098,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>8</v>
               </pt>
@@ -3411,13 +3121,7 @@
                 <v>4</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>4</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
+                <v>6</v>
               </pt>
             </numLit>
           </val>
@@ -3481,6 +3185,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3531,7 +3243,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3548,19 +3260,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>6</v>
               </pt>
@@ -3577,12 +3283,6 @@
                 <v>5</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3647,6 +3347,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3697,7 +3405,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3714,19 +3422,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -3743,12 +3445,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3813,6 +3509,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3863,7 +3567,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3880,19 +3584,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -3909,13 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
                 <v>2</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3979,6 +3671,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4029,7 +3729,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4046,19 +3746,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4075,12 +3769,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4145,6 +3833,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4195,7 +3891,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -4221,25 +3917,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4265,18 +3949,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4341,6 +4013,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4391,7 +4071,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4408,19 +4088,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -4437,12 +4111,6 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4507,6 +4175,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4568,7 +4244,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4649,6 +4325,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4710,7 +4394,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4791,6 +4475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4852,7 +4544,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4915,7 +4607,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -4933,6 +4625,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4994,7 +4694,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5075,6 +4775,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5136,7 +4844,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5217,6 +4925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5278,7 +4994,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5359,6 +5075,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5420,7 +5144,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5501,6 +5225,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5562,7 +5294,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5643,6 +5375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5704,7 +5444,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5767,7 +5507,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5785,6 +5525,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5835,7 +5583,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -5861,25 +5609,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -5905,19 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5981,6 +5705,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6042,7 +5774,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6105,7 +5837,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6123,6 +5855,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6173,23 +5913,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6253,6 +5999,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6303,23 +6057,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6383,6 +6143,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6433,23 +6201,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6513,6 +6287,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6563,23 +6345,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>11</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6643,6 +6431,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6693,23 +6489,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>22</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6773,6 +6575,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6823,23 +6633,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6885,7 +6701,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6903,6 +6719,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6953,23 +6777,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -7033,6 +6863,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7083,23 +6921,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>17</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -7163,6 +7007,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7213,22 +7065,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7293,6 +7151,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7343,7 +7209,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -7369,25 +7235,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -7413,19 +7267,7 @@
                 <v>2</v>
               </pt>
               <pt idx="8">
-                <v>9</v>
-              </pt>
-              <pt idx="9">
-                <v>7</v>
-              </pt>
-              <pt idx="10">
-                <v>4</v>
-              </pt>
-              <pt idx="11">
-                <v>2</v>
-              </pt>
-              <pt idx="12">
-                <v>2</v>
+                <v>24</v>
               </pt>
             </numLit>
           </val>
@@ -7471,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="12"/>
+          <max val="24"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7489,6 +7331,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7539,22 +7389,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7619,6 +7475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7669,22 +7533,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7749,6 +7619,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7799,22 +7677,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7879,6 +7763,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7929,22 +7821,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8009,6 +7907,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8059,23 +7965,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8139,6 +8051,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8189,23 +8109,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8251,7 +8177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8269,6 +8195,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8319,23 +8253,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8381,7 +8321,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8399,6 +8339,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8449,23 +8397,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8529,6 +8483,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8579,23 +8541,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8659,6 +8627,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8709,23 +8685,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -8789,6 +8771,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8839,7 +8829,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -8865,25 +8855,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -8909,19 +8887,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>3</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>1</v>
+                <v>7</v>
               </pt>
             </numLit>
           </val>
@@ -8985,6 +8951,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9035,22 +9009,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>高根　拓也</v>
               </pt>
               <pt idx="1">
                 <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -9115,6 +9095,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9254,6 +9242,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9393,6 +9389,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9532,6 +9536,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9671,6 +9683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9810,6 +9830,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9949,6 +9977,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10088,6 +10124,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10227,6 +10271,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10366,6 +10418,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10416,7 +10476,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10442,25 +10502,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10486,19 +10534,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>3</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
+                <v>4</v>
               </pt>
             </numLit>
           </val>
@@ -10544,7 +10580,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10562,6 +10598,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10701,6 +10745,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10751,7 +10803,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10777,25 +10829,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -10821,19 +10861,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>6</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -10879,7 +10907,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10897,6 +10925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10947,7 +10983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10973,25 +11009,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="11">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="12">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -11018,18 +11042,6 @@
               </pt>
               <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -11093,6 +11105,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11105,7 +11125,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11127,7 +11147,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11149,7 +11169,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11171,7 +11191,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11193,7 +11213,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11215,7 +11235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11237,7 +11257,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11259,7 +11279,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11281,7 +11301,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11303,7 +11323,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11330,7 +11350,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11352,7 +11372,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11374,7 +11394,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11396,7 +11416,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11418,7 +11438,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11440,7 +11460,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11462,7 +11482,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11484,7 +11504,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11506,7 +11526,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11528,7 +11548,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11555,7 +11575,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11577,7 +11597,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11599,7 +11619,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11621,7 +11641,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11643,7 +11663,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11665,7 +11685,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11687,7 +11707,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11709,7 +11729,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11731,7 +11751,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11753,7 +11773,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11780,7 +11800,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11802,7 +11822,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11824,7 +11844,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11846,7 +11866,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11868,7 +11888,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11890,7 +11910,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11912,7 +11932,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11934,7 +11954,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11956,7 +11976,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11978,7 +11998,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12005,7 +12025,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12027,7 +12047,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12049,7 +12069,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12071,7 +12091,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12093,7 +12113,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12115,7 +12135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12137,7 +12157,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12159,7 +12179,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12181,7 +12201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12203,7 +12223,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12230,7 +12250,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12252,7 +12272,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12274,7 +12294,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12296,7 +12316,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12318,7 +12338,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12340,7 +12360,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12362,7 +12382,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12384,7 +12404,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12406,7 +12426,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12428,7 +12448,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12455,7 +12475,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12477,7 +12497,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12499,7 +12519,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12521,7 +12541,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12543,7 +12563,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12565,7 +12585,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12587,7 +12607,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12609,7 +12629,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12631,7 +12651,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12653,7 +12673,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12960,7 +12980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -12978,10 +12998,6 @@
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12992,7 +13008,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13063,49 +13079,13 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>落
-合
-典
-彦</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -13138,20 +13118,8 @@
       <c r="Q4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -13182,22 +13150,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13230,20 +13186,8 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -13274,22 +13218,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -13320,19 +13252,7 @@
         <v>2</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -13366,19 +13286,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -13412,19 +13320,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -13458,19 +13354,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -13506,18 +13390,6 @@
       <c r="Q12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -13552,20 +13424,9 @@
       <c r="Q13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13578,7 +13439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -13594,11 +13455,6 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -13609,7 +13465,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13663,57 +13519,13 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -13740,23 +13552,8 @@
       <c r="O4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -13783,23 +13580,8 @@
       <c r="O5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13826,23 +13608,8 @@
       <c r="O6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -13869,23 +13636,8 @@
       <c r="O7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -13910,22 +13662,7 @@
         <v>2</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -13953,22 +13690,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -13998,21 +13720,6 @@
       <c r="O10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -14039,22 +13746,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14082,21 +13774,6 @@
         <v>0</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14127,23 +13804,9 @@
       <c r="O13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14156,7 +13819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14171,8 +13834,6 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14183,7 +13844,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14230,34 +13891,13 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>落
-合
-典
-彦</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14281,14 +13921,8 @@
       <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14312,14 +13946,8 @@
       <c r="N5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14343,14 +13971,8 @@
       <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14372,16 +13994,10 @@
         <v>3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14403,13 +14019,7 @@
         <v>4</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -14436,12 +14046,6 @@
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -14467,12 +14071,6 @@
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -14496,13 +14094,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14529,12 +14121,6 @@
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -14560,14 +14146,9 @@
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14603,7 +14184,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14636,18 +14217,13 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14666,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14685,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14704,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14723,7 +14299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14838,6 +14414,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14850,7 +14427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14861,6 +14438,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14871,7 +14449,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14893,8 +14471,15 @@
 一</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14906,8 +14491,11 @@
       <c r="J4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14919,8 +14507,11 @@
       <c r="J5" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14932,8 +14523,11 @@
       <c r="J6" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14945,8 +14539,11 @@
       <c r="J7" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14957,6 +14554,9 @@
       </c>
       <c r="J8" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14971,6 +14571,9 @@
       <c r="J9" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -14984,6 +14587,9 @@
       <c r="J10" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -14997,6 +14603,9 @@
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
@@ -15010,6 +14619,9 @@
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15023,8 +14635,12 @@
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15037,7 +14653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -15048,6 +14664,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -15058,7 +14675,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15080,8 +14697,15 @@
 一</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15093,8 +14717,11 @@
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15106,8 +14733,11 @@
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15119,8 +14749,11 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15132,8 +14765,11 @@
       <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15144,6 +14780,9 @@
       </c>
       <c r="J8" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15158,6 +14797,9 @@
       <c r="J9" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -15171,6 +14813,9 @@
       <c r="J10" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15184,6 +14829,9 @@
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
@@ -15197,6 +14845,9 @@
       <c r="J12" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15210,8 +14861,12 @@
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15248,7 +14903,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15294,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15316,7 +14971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15338,7 +14993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15360,7 +15015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15382,7 +15037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15515,6 +15170,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
